--- a/artfynd/A 35231-2026 artfynd.xlsx
+++ b/artfynd/A 35231-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137094213</v>
       </c>
       <c r="B2" t="n">
-        <v>92550</v>
+        <v>92556</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35231-2026 artfynd.xlsx
+++ b/artfynd/A 35231-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137094213</v>
       </c>
       <c r="B2" t="n">
-        <v>92556</v>
+        <v>92560</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137094209</v>
       </c>
       <c r="B3" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137094212</v>
       </c>
       <c r="B4" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137094217</v>
       </c>
       <c r="B5" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>137094219</v>
       </c>
       <c r="B6" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35231-2026 artfynd.xlsx
+++ b/artfynd/A 35231-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137094213</v>
       </c>
       <c r="B2" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137094209</v>
       </c>
       <c r="B3" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137094212</v>
       </c>
       <c r="B4" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137094217</v>
       </c>
       <c r="B5" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>137094219</v>
       </c>
       <c r="B6" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35231-2026 artfynd.xlsx
+++ b/artfynd/A 35231-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137094213</v>
       </c>
       <c r="B2" t="n">
-        <v>92562</v>
+        <v>92575</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137094209</v>
       </c>
       <c r="B3" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137094212</v>
       </c>
       <c r="B4" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137094217</v>
       </c>
       <c r="B5" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>137094219</v>
       </c>
       <c r="B6" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137094210</v>
       </c>
       <c r="B7" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 35231-2026 artfynd.xlsx
+++ b/artfynd/A 35231-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137094213</v>
       </c>
       <c r="B2" t="n">
-        <v>92575</v>
+        <v>92577</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137094209</v>
       </c>
       <c r="B3" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137094212</v>
       </c>
       <c r="B4" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137094217</v>
       </c>
       <c r="B5" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>137094219</v>
       </c>
       <c r="B6" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137094210</v>
       </c>
       <c r="B7" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>137094211</v>
       </c>
       <c r="B8" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
